--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C1A755-1EBD-46A6-8102-02866E04E641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61952259-705A-479C-8FBE-4C10018CB8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32250" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关卡|Level" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="123">
   <si>
     <t>##var</t>
   </si>
@@ -259,6 +259,171 @@
   </si>
   <si>
     <t>Level_55</t>
+  </si>
+  <si>
+    <t>Level_56</t>
+  </si>
+  <si>
+    <t>Level_57</t>
+  </si>
+  <si>
+    <t>Level_58</t>
+  </si>
+  <si>
+    <t>Level_59</t>
+  </si>
+  <si>
+    <t>Level_60</t>
+  </si>
+  <si>
+    <t>Level_61</t>
+  </si>
+  <si>
+    <t>Level_62</t>
+  </si>
+  <si>
+    <t>Level_63</t>
+  </si>
+  <si>
+    <t>Level_64</t>
+  </si>
+  <si>
+    <t>Level_65</t>
+  </si>
+  <si>
+    <t>Level_66</t>
+  </si>
+  <si>
+    <t>Level_67</t>
+  </si>
+  <si>
+    <t>Level_68</t>
+  </si>
+  <si>
+    <t>Level_69</t>
+  </si>
+  <si>
+    <t>Level_70</t>
+  </si>
+  <si>
+    <t>Level_71</t>
+  </si>
+  <si>
+    <t>Level_72</t>
+  </si>
+  <si>
+    <t>Level_73</t>
+  </si>
+  <si>
+    <t>Level_74</t>
+  </si>
+  <si>
+    <t>Level_75</t>
+  </si>
+  <si>
+    <t>Level_76</t>
+  </si>
+  <si>
+    <t>Level_77</t>
+  </si>
+  <si>
+    <t>Level_78</t>
+  </si>
+  <si>
+    <t>Level_79</t>
+  </si>
+  <si>
+    <t>Level_80</t>
+  </si>
+  <si>
+    <t>Level_81</t>
+  </si>
+  <si>
+    <t>Level_82</t>
+  </si>
+  <si>
+    <t>Level_83</t>
+  </si>
+  <si>
+    <t>Level_84</t>
+  </si>
+  <si>
+    <t>Level_85</t>
+  </si>
+  <si>
+    <t>Level_86</t>
+  </si>
+  <si>
+    <t>Level_87</t>
+  </si>
+  <si>
+    <t>Level_88</t>
+  </si>
+  <si>
+    <t>Level_89</t>
+  </si>
+  <si>
+    <t>Level_90</t>
+  </si>
+  <si>
+    <t>Level_91</t>
+  </si>
+  <si>
+    <t>Level_92</t>
+  </si>
+  <si>
+    <t>Level_93</t>
+  </si>
+  <si>
+    <t>Level_94</t>
+  </si>
+  <si>
+    <t>Level_95</t>
+  </si>
+  <si>
+    <t>Level_96</t>
+  </si>
+  <si>
+    <t>Level_97</t>
+  </si>
+  <si>
+    <t>Level_98</t>
+  </si>
+  <si>
+    <t>Level_99</t>
+  </si>
+  <si>
+    <t>Level_100</t>
+  </si>
+  <si>
+    <t>Level_101</t>
+  </si>
+  <si>
+    <t>Level_102</t>
+  </si>
+  <si>
+    <t>Level_103</t>
+  </si>
+  <si>
+    <t>Level_104</t>
+  </si>
+  <si>
+    <t>Level_105</t>
+  </si>
+  <si>
+    <t>Level_106</t>
+  </si>
+  <si>
+    <t>Level_107</t>
+  </si>
+  <si>
+    <t>Level_108</t>
+  </si>
+  <si>
+    <t>Level_109</t>
+  </si>
+  <si>
+    <t>Level_110</t>
   </si>
 </sst>
 </file>
@@ -660,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z59"/>
+  <dimension ref="A1:Z114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1417,6 +1582,611 @@
         <v>10002</v>
       </c>
     </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B60">
+        <v>56</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B61">
+        <v>57</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B62">
+        <v>58</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E62" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B63">
+        <v>59</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E63" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B64">
+        <v>60</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E64" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B65">
+        <v>61</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B66">
+        <v>62</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B67">
+        <v>63</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B68">
+        <v>64</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E68" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B69">
+        <v>65</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E69" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B70">
+        <v>66</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B71">
+        <v>67</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E71" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B72">
+        <v>68</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E72" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B73">
+        <v>69</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E73" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B74">
+        <v>70</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B75">
+        <v>71</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E75" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B76">
+        <v>72</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E76" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B77">
+        <v>73</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E77" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B78">
+        <v>74</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E78" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B79">
+        <v>75</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B80">
+        <v>76</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B81">
+        <v>77</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B82">
+        <v>78</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E82" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B83">
+        <v>79</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E83" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B84">
+        <v>80</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E84" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B85">
+        <v>81</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E85" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B86">
+        <v>82</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E86" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B87">
+        <v>83</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E87" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B88">
+        <v>84</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E88" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B89">
+        <v>85</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E89" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B90">
+        <v>86</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E90" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B91">
+        <v>87</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E91" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B92">
+        <v>88</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E92" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B93">
+        <v>89</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E93" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B94">
+        <v>90</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E94" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B95">
+        <v>91</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E95" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B96">
+        <v>92</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E96" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B97">
+        <v>93</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E97" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B98">
+        <v>94</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E98" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B99">
+        <v>95</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E99" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B100">
+        <v>96</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E100" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B101">
+        <v>97</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E101" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B102">
+        <v>98</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E102" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B103">
+        <v>99</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E103" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B104">
+        <v>100</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E104" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B105">
+        <v>101</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E105" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B106">
+        <v>102</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E106" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B107">
+        <v>103</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E107" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B108">
+        <v>104</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E108" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B109">
+        <v>105</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E109" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B110">
+        <v>106</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E110" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B111">
+        <v>107</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E111" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B112">
+        <v>108</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E112" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B113">
+        <v>109</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E113" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B114">
+        <v>110</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E114" s="6">
+        <v>10001</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61952259-705A-479C-8FBE-4C10018CB8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8190D935-B968-4D04-80E8-8B48460EE046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32250" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="169">
   <si>
     <t>##var</t>
   </si>
@@ -424,6 +424,144 @@
   </si>
   <si>
     <t>Level_110</t>
+  </si>
+  <si>
+    <t>Level_111</t>
+  </si>
+  <si>
+    <t>Level_112</t>
+  </si>
+  <si>
+    <t>Level_113</t>
+  </si>
+  <si>
+    <t>Level_114</t>
+  </si>
+  <si>
+    <t>Level_115</t>
+  </si>
+  <si>
+    <t>Level_116</t>
+  </si>
+  <si>
+    <t>Level_117</t>
+  </si>
+  <si>
+    <t>Level_118</t>
+  </si>
+  <si>
+    <t>Level_119</t>
+  </si>
+  <si>
+    <t>Level_120</t>
+  </si>
+  <si>
+    <t>Level_121</t>
+  </si>
+  <si>
+    <t>Level_122</t>
+  </si>
+  <si>
+    <t>Level_123</t>
+  </si>
+  <si>
+    <t>Level_124</t>
+  </si>
+  <si>
+    <t>Level_125</t>
+  </si>
+  <si>
+    <t>Level_126</t>
+  </si>
+  <si>
+    <t>Level_127</t>
+  </si>
+  <si>
+    <t>Level_128</t>
+  </si>
+  <si>
+    <t>Level_129</t>
+  </si>
+  <si>
+    <t>Level_130</t>
+  </si>
+  <si>
+    <t>Level_131</t>
+  </si>
+  <si>
+    <t>Level_132</t>
+  </si>
+  <si>
+    <t>Level_133</t>
+  </si>
+  <si>
+    <t>Level_134</t>
+  </si>
+  <si>
+    <t>Level_135</t>
+  </si>
+  <si>
+    <t>Level_136</t>
+  </si>
+  <si>
+    <t>Level_137</t>
+  </si>
+  <si>
+    <t>Level_138</t>
+  </si>
+  <si>
+    <t>Level_139</t>
+  </si>
+  <si>
+    <t>Level_140</t>
+  </si>
+  <si>
+    <t>Level_141</t>
+  </si>
+  <si>
+    <t>Level_142</t>
+  </si>
+  <si>
+    <t>Level_143</t>
+  </si>
+  <si>
+    <t>Level_144</t>
+  </si>
+  <si>
+    <t>Level_145</t>
+  </si>
+  <si>
+    <t>Level_146</t>
+  </si>
+  <si>
+    <t>Level_147</t>
+  </si>
+  <si>
+    <t>Level_148</t>
+  </si>
+  <si>
+    <t>Level_149</t>
+  </si>
+  <si>
+    <t>Level_150</t>
+  </si>
+  <si>
+    <t>Level_151</t>
+  </si>
+  <si>
+    <t>Level_152</t>
+  </si>
+  <si>
+    <t>Level_153</t>
+  </si>
+  <si>
+    <t>Level_154</t>
+  </si>
+  <si>
+    <t>Level_155</t>
+  </si>
+  <si>
+    <t>Level_156</t>
   </si>
 </sst>
 </file>
@@ -825,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z114"/>
+  <dimension ref="A1:Z160"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -2187,6 +2325,512 @@
         <v>10001</v>
       </c>
     </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B115">
+        <v>111</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E115" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B116">
+        <v>112</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E116" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B117">
+        <v>113</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E117" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B118">
+        <v>114</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E118" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B119">
+        <v>115</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E119" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B120">
+        <v>116</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E120" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B121">
+        <v>117</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E121" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B122">
+        <v>118</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E122" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B123">
+        <v>119</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E123" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B124">
+        <v>120</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E124" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B125">
+        <v>121</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E125" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B126">
+        <v>122</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E126" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B127">
+        <v>123</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E127" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B128">
+        <v>124</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E128" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B129">
+        <v>125</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E129" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B130">
+        <v>126</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E130" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B131">
+        <v>127</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E131" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B132">
+        <v>128</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E132" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B133">
+        <v>129</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E133" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B134">
+        <v>130</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E134" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B135">
+        <v>131</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E135" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B136">
+        <v>132</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E136" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B137">
+        <v>133</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E137" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B138">
+        <v>134</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E138" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B139">
+        <v>135</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E139" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B140">
+        <v>136</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E140" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B141">
+        <v>137</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E141" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B142">
+        <v>138</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E142" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B143">
+        <v>139</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E143" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B144">
+        <v>140</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E144" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B145">
+        <v>141</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E145" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B146">
+        <v>142</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E146" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B147">
+        <v>143</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E147" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B148">
+        <v>144</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E148" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B149">
+        <v>145</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E149" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B150">
+        <v>146</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E150" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B151">
+        <v>147</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E151" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B152">
+        <v>148</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E152" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B153">
+        <v>149</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E153" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B154">
+        <v>150</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E154" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B155">
+        <v>151</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E155" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B156">
+        <v>152</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E156" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B157">
+        <v>153</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E157" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B158">
+        <v>154</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E158" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B159">
+        <v>155</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E159" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B160">
+        <v>156</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E160" s="6">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8190D935-B968-4D04-80E8-8B48460EE046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2362EF1-0003-430D-A836-9D01560DE879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32250" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关卡|Level" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="214">
   <si>
     <t>##var</t>
   </si>
@@ -562,6 +562,141 @@
   </si>
   <si>
     <t>Level_156</t>
+  </si>
+  <si>
+    <t>Level_157</t>
+  </si>
+  <si>
+    <t>Level_158</t>
+  </si>
+  <si>
+    <t>Level_159</t>
+  </si>
+  <si>
+    <t>Level_160</t>
+  </si>
+  <si>
+    <t>Level_161</t>
+  </si>
+  <si>
+    <t>Level_162</t>
+  </si>
+  <si>
+    <t>Level_163</t>
+  </si>
+  <si>
+    <t>Level_164</t>
+  </si>
+  <si>
+    <t>Level_165</t>
+  </si>
+  <si>
+    <t>Level_166</t>
+  </si>
+  <si>
+    <t>Level_167</t>
+  </si>
+  <si>
+    <t>Level_168</t>
+  </si>
+  <si>
+    <t>Level_169</t>
+  </si>
+  <si>
+    <t>Level_170</t>
+  </si>
+  <si>
+    <t>Level_171</t>
+  </si>
+  <si>
+    <t>Level_172</t>
+  </si>
+  <si>
+    <t>Level_173</t>
+  </si>
+  <si>
+    <t>Level_174</t>
+  </si>
+  <si>
+    <t>Level_175</t>
+  </si>
+  <si>
+    <t>Level_176</t>
+  </si>
+  <si>
+    <t>Level_177</t>
+  </si>
+  <si>
+    <t>Level_178</t>
+  </si>
+  <si>
+    <t>Level_179</t>
+  </si>
+  <si>
+    <t>Level_180</t>
+  </si>
+  <si>
+    <t>Level_181</t>
+  </si>
+  <si>
+    <t>Level_182</t>
+  </si>
+  <si>
+    <t>Level_183</t>
+  </si>
+  <si>
+    <t>Level_184</t>
+  </si>
+  <si>
+    <t>Level_185</t>
+  </si>
+  <si>
+    <t>Level_186</t>
+  </si>
+  <si>
+    <t>Level_187</t>
+  </si>
+  <si>
+    <t>Level_188</t>
+  </si>
+  <si>
+    <t>Level_189</t>
+  </si>
+  <si>
+    <t>Level_190</t>
+  </si>
+  <si>
+    <t>Level_191</t>
+  </si>
+  <si>
+    <t>Level_192</t>
+  </si>
+  <si>
+    <t>Level_193</t>
+  </si>
+  <si>
+    <t>Level_194</t>
+  </si>
+  <si>
+    <t>Level_195</t>
+  </si>
+  <si>
+    <t>Level_196</t>
+  </si>
+  <si>
+    <t>Level_197</t>
+  </si>
+  <si>
+    <t>Level_198</t>
+  </si>
+  <si>
+    <t>Level_199</t>
+  </si>
+  <si>
+    <t>Level_200</t>
+  </si>
+  <si>
+    <t>Level_201</t>
   </si>
 </sst>
 </file>
@@ -963,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z160"/>
+  <dimension ref="A1:Z205"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -2831,6 +2966,501 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B161">
+        <v>157</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E161" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B162">
+        <v>158</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E162" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B163">
+        <v>159</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E163" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B164">
+        <v>160</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E164" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B165">
+        <v>161</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E165" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B166">
+        <v>162</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E166" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B167">
+        <v>163</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E167" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B168">
+        <v>164</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E168" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B169">
+        <v>165</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E169" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B170">
+        <v>166</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E170" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B171">
+        <v>167</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E171" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B172">
+        <v>168</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E172" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B173">
+        <v>169</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E173" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B174">
+        <v>170</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E174" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B175">
+        <v>171</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E175" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B176">
+        <v>172</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E176" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B177">
+        <v>173</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E177" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B178">
+        <v>174</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E178" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="179" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B179">
+        <v>175</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E179" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B180">
+        <v>176</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E180" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="181" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B181">
+        <v>177</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E181" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B182">
+        <v>178</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E182" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B183">
+        <v>179</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E183" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B184">
+        <v>180</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E184" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="185" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B185">
+        <v>181</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E185" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="186" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B186">
+        <v>182</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E186" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="187" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B187">
+        <v>183</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E187" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="188" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B188">
+        <v>184</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E188" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="189" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B189">
+        <v>185</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E189" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="190" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B190">
+        <v>186</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E190" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="191" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B191">
+        <v>187</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E191" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="192" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B192">
+        <v>188</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E192" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="193" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B193">
+        <v>189</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E193" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="194" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B194">
+        <v>190</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E194" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="195" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B195">
+        <v>191</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E195" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B196">
+        <v>192</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E196" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="197" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B197">
+        <v>193</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E197" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="198" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B198">
+        <v>194</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E198" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="199" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B199">
+        <v>195</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E199" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="200" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B200">
+        <v>196</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E200" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="201" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B201">
+        <v>197</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E201" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="202" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B202">
+        <v>198</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E202" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="203" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B203">
+        <v>199</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E203" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B204">
+        <v>200</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E204" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="205" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B205">
+        <v>201</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E205" s="6">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2362EF1-0003-430D-A836-9D01560DE879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7144A91F-7CC8-47AB-ACB2-32AD1E376DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="247">
   <si>
     <t>##var</t>
   </si>
@@ -697,6 +697,105 @@
   </si>
   <si>
     <t>Level_201</t>
+  </si>
+  <si>
+    <t>Level_202</t>
+  </si>
+  <si>
+    <t>Level_203</t>
+  </si>
+  <si>
+    <t>Level_204</t>
+  </si>
+  <si>
+    <t>Level_205</t>
+  </si>
+  <si>
+    <t>Level_206</t>
+  </si>
+  <si>
+    <t>Level_207</t>
+  </si>
+  <si>
+    <t>Level_208</t>
+  </si>
+  <si>
+    <t>Level_209</t>
+  </si>
+  <si>
+    <t>Level_210</t>
+  </si>
+  <si>
+    <t>Level_211</t>
+  </si>
+  <si>
+    <t>Level_212</t>
+  </si>
+  <si>
+    <t>Level_213</t>
+  </si>
+  <si>
+    <t>Level_214</t>
+  </si>
+  <si>
+    <t>Level_215</t>
+  </si>
+  <si>
+    <t>Level_216</t>
+  </si>
+  <si>
+    <t>Level_217</t>
+  </si>
+  <si>
+    <t>Level_218</t>
+  </si>
+  <si>
+    <t>Level_219</t>
+  </si>
+  <si>
+    <t>Level_220</t>
+  </si>
+  <si>
+    <t>Level_221</t>
+  </si>
+  <si>
+    <t>Level_222</t>
+  </si>
+  <si>
+    <t>Level_223</t>
+  </si>
+  <si>
+    <t>Level_224</t>
+  </si>
+  <si>
+    <t>Level_225</t>
+  </si>
+  <si>
+    <t>Level_226</t>
+  </si>
+  <si>
+    <t>Level_227</t>
+  </si>
+  <si>
+    <t>Level_228</t>
+  </si>
+  <si>
+    <t>Level_229</t>
+  </si>
+  <si>
+    <t>Level_230</t>
+  </si>
+  <si>
+    <t>Level_231</t>
+  </si>
+  <si>
+    <t>Level_232</t>
+  </si>
+  <si>
+    <t>Level_233</t>
+  </si>
+  <si>
+    <t>Level_234</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z205"/>
+  <dimension ref="A1:Z238"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -3461,6 +3560,369 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B206">
+        <v>202</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E206" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B207">
+        <v>203</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E207" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B208">
+        <v>204</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E208" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B209">
+        <v>205</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E209" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B210">
+        <v>206</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E210" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="211" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B211">
+        <v>207</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E211" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B212">
+        <v>208</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E212" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="213" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B213">
+        <v>209</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E213" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="214" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B214">
+        <v>210</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E214" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="215" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B215">
+        <v>211</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E215" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="216" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B216">
+        <v>212</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E216" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="217" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B217">
+        <v>213</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E217" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B218">
+        <v>214</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E218" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="219" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B219">
+        <v>215</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E219" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="220" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B220">
+        <v>216</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E220" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="221" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B221">
+        <v>217</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E221" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="222" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B222">
+        <v>218</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E222" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="223" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B223">
+        <v>219</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E223" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="224" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B224">
+        <v>220</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E224" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="225" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B225">
+        <v>221</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E225" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="226" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B226">
+        <v>222</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E226" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="227" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B227">
+        <v>223</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E227" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="228" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B228">
+        <v>224</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="E228" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="229" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B229">
+        <v>225</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E229" s="6">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="230" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B230">
+        <v>226</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E230" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="231" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B231">
+        <v>227</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E231" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="232" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B232">
+        <v>228</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E232" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="233" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B233">
+        <v>229</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E233" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="234" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B234">
+        <v>230</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E234" s="6">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="235" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B235">
+        <v>231</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E235" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="236" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B236">
+        <v>232</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E236" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="237" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B237">
+        <v>233</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E237" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="238" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B238">
+        <v>234</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E238" s="6">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TEngine/Configs/GameConfig/Datas/Level.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Level.xlsx
@@ -1355,7 +1355,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="6">
-        <v>10001</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
@@ -1401,7 +1401,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
@@ -1511,7 +1511,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
@@ -1566,7 +1566,7 @@
         <v>32</v>
       </c>
       <c r="E24" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
@@ -1621,7 +1621,7 @@
         <v>37</v>
       </c>
       <c r="E29" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
@@ -1731,7 +1731,7 @@
         <v>47</v>
       </c>
       <c r="E39" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
@@ -1786,7 +1786,7 @@
         <v>52</v>
       </c>
       <c r="E44" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.2">
@@ -1841,7 +1841,7 @@
         <v>57</v>
       </c>
       <c r="E49" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.2">
@@ -1951,7 +1951,7 @@
         <v>67</v>
       </c>
       <c r="E59" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.2">
@@ -2006,7 +2006,7 @@
         <v>72</v>
       </c>
       <c r="E64" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
@@ -2061,7 +2061,7 @@
         <v>77</v>
       </c>
       <c r="E69" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.2">
@@ -2171,7 +2171,7 @@
         <v>87</v>
       </c>
       <c r="E79" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.2">
@@ -2226,7 +2226,7 @@
         <v>92</v>
       </c>
       <c r="E84" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.2">
@@ -2281,7 +2281,7 @@
         <v>97</v>
       </c>
       <c r="E89" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.2">
@@ -2391,7 +2391,7 @@
         <v>107</v>
       </c>
       <c r="E99" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.2">
@@ -2446,7 +2446,7 @@
         <v>112</v>
       </c>
       <c r="E104" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.2">
@@ -2501,7 +2501,7 @@
         <v>117</v>
       </c>
       <c r="E109" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.2">
@@ -2611,7 +2611,7 @@
         <v>127</v>
       </c>
       <c r="E119" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.2">
@@ -2666,7 +2666,7 @@
         <v>132</v>
       </c>
       <c r="E124" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.2">
@@ -2721,7 +2721,7 @@
         <v>137</v>
       </c>
       <c r="E129" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.2">
@@ -2831,7 +2831,7 @@
         <v>147</v>
       </c>
       <c r="E139" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.2">
@@ -2886,7 +2886,7 @@
         <v>152</v>
       </c>
       <c r="E144" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.2">
@@ -2941,7 +2941,7 @@
         <v>157</v>
       </c>
       <c r="E149" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.2">
@@ -3051,7 +3051,7 @@
         <v>167</v>
       </c>
       <c r="E159" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.2">
@@ -3106,7 +3106,7 @@
         <v>172</v>
       </c>
       <c r="E164" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.2">
@@ -3161,7 +3161,7 @@
         <v>177</v>
       </c>
       <c r="E169" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.2">
@@ -3271,7 +3271,7 @@
         <v>187</v>
       </c>
       <c r="E179" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.2">
@@ -3326,7 +3326,7 @@
         <v>192</v>
       </c>
       <c r="E184" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.2">
@@ -3381,7 +3381,7 @@
         <v>197</v>
       </c>
       <c r="E189" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="190" spans="2:5" x14ac:dyDescent="0.2">
@@ -3491,7 +3491,7 @@
         <v>207</v>
       </c>
       <c r="E199" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="200" spans="2:5" x14ac:dyDescent="0.2">
@@ -3546,7 +3546,7 @@
         <v>212</v>
       </c>
       <c r="E204" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.2">
@@ -3601,7 +3601,7 @@
         <v>217</v>
       </c>
       <c r="E209" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="210" spans="2:5" x14ac:dyDescent="0.2">
@@ -3711,7 +3711,7 @@
         <v>227</v>
       </c>
       <c r="E219" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="220" spans="2:5" x14ac:dyDescent="0.2">
@@ -3766,7 +3766,7 @@
         <v>232</v>
       </c>
       <c r="E224" s="6">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="225" spans="2:5" x14ac:dyDescent="0.2">
@@ -3821,7 +3821,7 @@
         <v>237</v>
       </c>
       <c r="E229" s="6">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.2">
